--- a/miami-dashboard/public/data/latest.xlsx
+++ b/miami-dashboard/public/data/latest.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -550,13 +550,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10664</v>
+        <v>10594</v>
       </c>
       <c r="G2" t="n">
-        <v>5337</v>
+        <v>4992</v>
       </c>
       <c r="H2" t="n">
-        <v>2437</v>
+        <v>2568</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -568,7 +568,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>511.82</v>
+        <v>508.78</v>
       </c>
       <c r="M2" t="n">
         <v>16447</v>
@@ -577,7 +577,7 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>500</v>
+        <v>680</v>
       </c>
     </row>
     <row r="3">
@@ -588,17 +588,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HS0002-2</t>
+          <t>HS0002-BOX</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B09RSSL9S7</t>
+          <t>B0997T27H8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HS0002-Master</t>
+          <t>HS0002-Bulk-Master</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -607,34 +607,34 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>195</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>170</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I3" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>13.77</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>391</v>
+        <v>70</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>180</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
@@ -645,17 +645,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HS0002-BOX</t>
+          <t>HB0024</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0997T27H8</t>
+          <t>B0D268LC2Z</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HS0002-Bulk-Master</t>
+          <t>HB0024</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -664,34 +664,34 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>343</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>540</v>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.94</v>
+        <v>40.04</v>
       </c>
       <c r="M4" t="n">
-        <v>70</v>
+        <v>1057</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>40</v>
+        <v>650</v>
       </c>
     </row>
     <row r="5">
@@ -702,17 +702,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HB0024</t>
+          <t>HB0016</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0D268LC2Z</t>
+          <t>B0BG3GN7J4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HB0024</t>
+          <t>HB0006-Master</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -721,34 +721,34 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>358</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>40.3</v>
+        <v>1.83</v>
       </c>
       <c r="M5" t="n">
-        <v>1057</v>
+        <v>58</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>590</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -759,17 +759,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HB0016</t>
+          <t>JOJOBA-10-DB</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0BG3GN7J4</t>
+          <t>B0CQ58JJGC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HB0006-Master</t>
+          <t>JOJOBA-Master</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -778,34 +778,34 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I6" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J6" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>4.29</v>
       </c>
       <c r="M6" t="n">
-        <v>58</v>
+        <v>129</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -816,53 +816,53 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JOJOBA-10-DB</t>
+          <t>JOJOBA-125</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0CQ58JJGC</t>
+          <t>B096G67XBL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>JOJOBA-Master</t>
+          <t>EO-JOJOBA-Master</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>EO</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="J7" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4.36</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -873,53 +873,53 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JOJOBA-125</t>
+          <t>JOJOBA-120</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B096G67XBL</t>
+          <t>B08S3G9NJZ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EO-JOJOBA-Master</t>
+          <t>JOJOBA-Master</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EO</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1.21</v>
+        <v>0.98</v>
       </c>
       <c r="M8" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -967,7 +967,7 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="M9" t="n">
         <v>98</v>
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2513</v>
+        <v>2483</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I11" t="n">
         <v>27</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>95.70999999999999</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="M11" t="n">
         <v>2649</v>
@@ -1090,7 +1090,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>910</v>
+        <v>930</v>
       </c>
     </row>
     <row r="12">
@@ -1126,19 +1126,19 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>7.27</v>
+        <v>7.21</v>
       </c>
       <c r="M12" t="n">
         <v>214</v>
@@ -1177,25 +1177,25 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
       </c>
       <c r="H13" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J13" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>4.51</v>
+        <v>4.72</v>
       </c>
       <c r="M13" t="n">
         <v>117</v>
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14">
@@ -1252,7 +1252,7 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="M14" t="n">
         <v>133</v>
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="M15" t="n">
         <v>53</v>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
         <v>8</v>
@@ -1366,7 +1366,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="M16" t="n">
         <v>48</v>
@@ -1386,53 +1386,53 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PD-LEMON-MCT-10-RL</t>
+          <t>EO-ROSEHIP-1.7oz-RL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0FX7MFNQZ</t>
+          <t>B0GK4X72YF</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PD-MCT-10-RL-Master</t>
+          <t>EO-1.7oz-RL-Master</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>EO</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2.83</v>
+        <v>2.12</v>
       </c>
       <c r="M17" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="N17" t="b">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EO-ROSEHIP-1.7oz-RL</t>
+          <t>EO-JOJOBA-1.7oz-RL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0GK4X72YF</t>
+          <t>B0GK6LJ56Z</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>20</v>
-      </c>
-      <c r="J18" t="n">
-        <v>20</v>
-      </c>
-      <c r="K18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="M18" t="n">
-        <v>95</v>
-      </c>
-      <c r="N18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EO-JOJOBA-1.7oz-RL</t>
+          <t>EO-COCONUT-1.7oz-RL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0GK6LJ56Z</t>
+          <t>B0GK711CCZ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EO-COCONUT-1.7oz-RL</t>
+          <t>EO-ARGAN-1.7oz-RL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0GK711CCZ</t>
+          <t>B0GK6R6NV8</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1576,34 +1576,34 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N20" t="b">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -1614,53 +1614,49 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EO-ARGAN-1.7oz-RL</t>
+          <t>PD-6PC-SET1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0GK6R6NV8</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>EO-1.7oz-RL-Master</t>
-        </is>
-      </c>
+          <t>B0G565921D</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EO</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N21" t="b">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -1671,12 +1667,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PD-6PC-SET1</t>
+          <t>PD-3PC-SET2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0G565921D</t>
+          <t>B0G56BTRJ2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1719,54 +1715,58 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>URGENT FBA</t>
+          <t>PLANNED FBA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PD-3PC-SET2</t>
+          <t>HS0002-2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0G56BTRJ2</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>B09RSSL9S7</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HS0002-Master</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="M23" t="n">
+        <v>391</v>
+      </c>
+      <c r="N23" t="b">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="b">
-        <v>0</v>
-      </c>
       <c r="O23" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
@@ -1796,13 +1796,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G24" t="n">
         <v>200</v>
       </c>
       <c r="H24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I24" t="n">
         <v>30</v>
@@ -1814,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>8.880000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="M24" t="n">
         <v>270</v>
@@ -1823,7 +1823,7 @@
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25">
@@ -1853,25 +1853,25 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G25" t="n">
         <v>160</v>
       </c>
       <c r="H25" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I25" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="J25" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>9.83</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="M25" t="n">
         <v>275</v>
@@ -1880,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
@@ -1891,53 +1891,53 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JOJOBA-120</t>
+          <t>EO-CASTOR-1oz</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B08S3G9NJZ</t>
+          <t>B0CZD3ZL5S</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>JOJOBA-Master</t>
+          <t>EO-CASTOR-Master</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>EO</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>25</v>
+        <v>396</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>594</v>
       </c>
       <c r="H26" t="n">
+        <v>458</v>
+      </c>
+      <c r="I26" t="n">
+        <v>45</v>
+      </c>
+      <c r="J26" t="n">
+        <v>45</v>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>40.34</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1207</v>
+      </c>
+      <c r="N26" t="b">
         <v>1</v>
       </c>
-      <c r="I26" t="n">
-        <v>30</v>
-      </c>
-      <c r="J26" t="n">
-        <v>30</v>
-      </c>
-      <c r="K26" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="M26" t="n">
-        <v>30</v>
-      </c>
-      <c r="N26" t="b">
-        <v>0</v>
-      </c>
       <c r="O26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
@@ -1948,110 +1948,110 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EO-CASTOR-1oz</t>
+          <t>PD-FRANK-CASTOR-MCT-10-RL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0CZD3ZL5S</t>
+          <t>B0FX6N2DPN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EO-CASTOR-Master</t>
+          <t>PD-MCT-10-RL-Master</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>EO</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>412</v>
+        <v>246</v>
       </c>
       <c r="G27" t="n">
-        <v>594</v>
+        <v>140</v>
       </c>
       <c r="H27" t="n">
-        <v>333</v>
+        <v>59</v>
       </c>
       <c r="I27" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>40.82</v>
+        <v>16.25</v>
       </c>
       <c r="M27" t="n">
-        <v>1207</v>
+        <v>522</v>
       </c>
       <c r="N27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PLANNED FBA</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PD-FRANK-CASTOR-MCT-10-RL</t>
+          <t>GK0487</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0FX6N2DPN</t>
+          <t>B07DT6ZDP5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PD-MCT-10-RL-Master</t>
+          <t>GK0486-Master</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>267</v>
+        <v>783</v>
       </c>
       <c r="G28" t="n">
-        <v>140</v>
+        <v>264</v>
       </c>
       <c r="H28" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="I28" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>16.49</v>
+        <v>41.32</v>
       </c>
       <c r="M28" t="n">
-        <v>522</v>
+        <v>1206</v>
       </c>
       <c r="N28" t="b">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>170</v>
+        <v>540</v>
       </c>
     </row>
     <row r="29">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GK0487</t>
+          <t>GK0712</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B07DT6ZDP5</t>
+          <t>B0853DNCBX</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2081,34 +2081,34 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>802</v>
+        <v>7</v>
       </c>
       <c r="G29" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>19.4</v>
+        <v>1</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>41.3</v>
+        <v>7.26</v>
       </c>
       <c r="M29" t="n">
-        <v>1206</v>
+        <v>207</v>
       </c>
       <c r="N29" t="b">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>540</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GK0712</t>
+          <t>GK0907</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0853DNCBX</t>
+          <t>B09BVWYFN3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2138,34 +2138,34 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>127</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>7.29</v>
+        <v>7.71</v>
       </c>
       <c r="M30" t="n">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="N30" t="b">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>280</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GK0907</t>
+          <t>GK0910</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B09BVWYFN3</t>
+          <t>B09CDZBKQ7</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2195,34 +2195,34 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
+        <v>13</v>
+      </c>
+      <c r="I31" t="n">
         <v>12</v>
       </c>
-      <c r="I31" t="n">
-        <v>17</v>
-      </c>
       <c r="J31" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>7.89</v>
+        <v>4.91</v>
       </c>
       <c r="M31" t="n">
-        <v>212</v>
+        <v>138</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GK0910</t>
+          <t>GK0874</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B09CDZBKQ7</t>
+          <t>B08LGHTD3N</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2252,34 +2252,34 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>4.89</v>
+        <v>1.7</v>
       </c>
       <c r="M32" t="n">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>140</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GK0874</t>
+          <t>GK0875</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B08LGHTD3N</t>
+          <t>B08LG6DCM7</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2309,34 +2309,34 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M33" t="n">
+        <v>73</v>
+      </c>
+      <c r="N33" t="b">
         <v>1</v>
       </c>
-      <c r="L33" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="M33" t="n">
-        <v>58</v>
-      </c>
-      <c r="N33" t="b">
-        <v>0</v>
-      </c>
       <c r="O33" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -2347,12 +2347,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GK0875</t>
+          <t>GK0873</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B08LG6DCM7</t>
+          <t>B08L8VZHKR</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2366,34 +2366,34 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>2.35</v>
+        <v>1.66</v>
       </c>
       <c r="M34" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="N34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GK0873</t>
+          <t>GK0752</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B08L8VZHKR</t>
+          <t>B086WR7VHX</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2423,34 +2423,34 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>3</v>
       </c>
       <c r="I35" t="n">
+        <v>38</v>
+      </c>
+      <c r="J35" t="n">
+        <v>38</v>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M35" t="n">
+        <v>66</v>
+      </c>
+      <c r="N35" t="b">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
         <v>20</v>
-      </c>
-      <c r="J35" t="n">
-        <v>20</v>
-      </c>
-      <c r="K35" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="M35" t="n">
-        <v>57</v>
-      </c>
-      <c r="N35" t="b">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="36">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GK0752</t>
+          <t>GK0751</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B086WR7VHX</t>
+          <t>B086WQ2W1W</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2480,34 +2480,34 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I36" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="M36" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GK0751</t>
+          <t>GK0909</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B086WQ2W1W</t>
+          <t>B09CF1TS13</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2537,34 +2537,34 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I37" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>2.47</v>
+        <v>1.02</v>
       </c>
       <c r="M37" t="n">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="N37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GK0909</t>
+          <t>GK0713</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B09CF1TS13</t>
+          <t>B0858HY34T</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2594,34 +2594,34 @@
         </is>
       </c>
       <c r="F38" t="n">
+        <v>19</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>17</v>
+      </c>
+      <c r="J38" t="n">
+        <v>17</v>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="M38" t="n">
         <v>32</v>
       </c>
-      <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" t="n">
-        <v>3</v>
-      </c>
-      <c r="I38" t="n">
-        <v>27</v>
-      </c>
-      <c r="J38" t="n">
-        <v>27</v>
-      </c>
-      <c r="K38" t="b">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="M38" t="n">
-        <v>37</v>
-      </c>
       <c r="N38" t="b">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GK0713</t>
+          <t>GK0529</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0858HY34T</t>
+          <t>B07J2XKY7G</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -2660,19 +2660,19 @@
         <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K39" t="b">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1.09</v>
+        <v>1.65</v>
       </c>
       <c r="M39" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="N39" t="b">
         <v>0</v>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GK0529</t>
+          <t>GK0872</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B07J2XKY7G</t>
+          <t>B08L8TPC7V</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2708,55 +2708,55 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1.66</v>
+        <v>1.22</v>
       </c>
       <c r="M40" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="N40" t="b">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>STEEL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GK0872</t>
+          <t>GK0693_FBA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B08L8TPC7V</t>
+          <t>B07RYJGHLJ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GK0486-Master</t>
+          <t>GK0541-Master</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2765,34 +2765,34 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J41" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="M41" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="N41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GK0693_FBA</t>
+          <t>GK0697_FBA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B07RYJGHLJ</t>
+          <t>B07RZHBXPL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2822,34 +2822,34 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="b">
         <v>1</v>
       </c>
-      <c r="I42" t="n">
-        <v>37</v>
-      </c>
-      <c r="J42" t="n">
-        <v>37</v>
-      </c>
-      <c r="K42" t="b">
-        <v>0</v>
-      </c>
       <c r="L42" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="N42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GK0697_FBA</t>
+          <t>GK0542_FBA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B07RZHBXPL</t>
+          <t>B07N8MTH3R</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2879,34 +2879,34 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="N43" t="b">
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GK0542_FBA</t>
+          <t>GK0694_FBA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B07N8MTH3R</t>
+          <t>B07RXGQ952</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2936,34 +2936,34 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I44" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J44" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1.26</v>
+        <v>2.2</v>
       </c>
       <c r="M44" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="N44" t="b">
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GK0694_FBA</t>
+          <t>GK0543_FBA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B07RXGQ952</t>
+          <t>B07N8MQXNP</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2993,34 +2993,34 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="M45" t="n">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="N45" t="b">
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46">
@@ -3031,17 +3031,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GK0543_FBA</t>
+          <t>GK0843_FBA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B07N8MQXNP</t>
+          <t>B089N85VYV</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>GK0541-Master</t>
+          <t>GK0715-Master</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3050,34 +3050,34 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N46" t="b">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GK0715_FBA</t>
+          <t>GK0839_FBA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B085SYXFDV</t>
+          <t>B089N8292Z</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3107,34 +3107,34 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>6.73</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="N47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
@@ -3145,12 +3145,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GK0843_FBA</t>
+          <t>GK0716_FBA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B089N85VYV</t>
+          <t>B085SYYYQV</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GK0839_FBA</t>
+          <t>GK0840_FBA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B089N8292Z</t>
+          <t>B089NHG1L1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3239,16 +3239,16 @@
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N49" t="b">
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GK0716_FBA</t>
+          <t>GK0717_FBA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B085SYYYQV</t>
+          <t>B085T5Z4PT</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3305,120 +3305,6 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>STEEL</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>GK0840_FBA</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>B089NHG1L1</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>GK0715-Master</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>GK</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="b">
-        <v>1</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M51" t="n">
-        <v>19</v>
-      </c>
-      <c r="N51" t="b">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>STEEL</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>GK0717_FBA</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>B085T5Z4PT</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>GK0715-Master</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>GK</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="b">
-        <v>1</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="b">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
         <v>20</v>
       </c>
     </row>
@@ -3465,10 +3351,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>3090</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="3">
@@ -3481,7 +3367,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>490</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4">
@@ -3504,10 +3390,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>340</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6">
@@ -3517,10 +3403,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C6" t="n">
-        <v>5330</v>
+        <v>5180</v>
       </c>
     </row>
   </sheetData>
